--- a/Product_Data_File/run_registry.xlsx
+++ b/Product_Data_File/run_registry.xlsx
@@ -14,24 +14,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>serial_number</t>
   </si>
   <si>
+    <t>program</t>
+  </si>
+  <si>
+    <t>space_vehicle</t>
+  </si>
+  <si>
     <t>run_date</t>
   </si>
   <si>
     <t>run_folder</t>
   </si>
   <si>
-    <t>SN 1122</t>
-  </si>
-  <si>
-    <t>2025-10-29 15:34:38</t>
-  </si>
-  <si>
-    <t>Product_Data_File\run_data\20251029_153438</t>
+    <t>SN_Insight_SV1_sn9911</t>
+  </si>
+  <si>
+    <t>Insight</t>
+  </si>
+  <si>
+    <t>SV1</t>
+  </si>
+  <si>
+    <t>2025-11-03 12:34:10</t>
+  </si>
+  <si>
+    <t>Product_Data_File\run_data\20251103_123410</t>
   </si>
 </sst>
 </file>
@@ -389,15 +401,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -407,16 +420,28 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
